--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487584_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487584_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0352</v>
+        <v>3.9703</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8987</v>
+        <v>2.6975</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1365</v>
+        <v>1.2728</v>
       </c>
       <c r="G2" t="n">
         <v>1.0323</v>
@@ -610,13 +610,13 @@
         <v>2.1344</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3044</v>
+        <v>0.2395</v>
       </c>
       <c r="T2" t="n">
-        <v>1.578</v>
+        <v>0.3768</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2736</v>
+        <v>-0.1374</v>
       </c>
       <c r="V2" t="n">
         <v>0.5642</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>G. TCHIRAKADZE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1974</v>
+        <v>2.8579</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8107</v>
+        <v>2.2668</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6133</v>
+        <v>0.5911</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9322</v>
+        <v>2.871</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9872</v>
+        <v>2.2393</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.055</v>
+        <v>0.6318</v>
       </c>
       <c r="J3" t="n">
-        <v>1.746</v>
+        <v>3.8187</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7054</v>
+        <v>2.6364</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0406</v>
+        <v>1.1823</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8138</v>
+        <v>-0.9477</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2817</v>
+        <v>-0.3971</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0956</v>
+        <v>-0.5506</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5224</v>
+        <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4309</v>
+        <v>0.1525</v>
       </c>
       <c r="T3" t="n">
-        <v>0.305</v>
+        <v>-0.2042</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1259</v>
+        <v>0.3567</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2821</v>
+        <v>-0.9418</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7298</v>
+        <v>-0.3776</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.4477</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4733</v>
+        <v>2.8243</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7441</v>
+        <v>3.4103</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2174</v>
+        <v>-0.586</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7055</v>
+        <v>0.9322</v>
       </c>
       <c r="H4" t="n">
-        <v>2.376</v>
+        <v>1.9872</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6706</v>
+        <v>-1.055</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4145</v>
+        <v>1.746</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1174</v>
+        <v>1.7054</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.7029</v>
+        <v>0.0406</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.709</v>
+        <v>-0.8138</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2587</v>
+        <v>0.2817</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9677</v>
+        <v>-1.0956</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5821</v>
+        <v>1.5523</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2985</v>
+        <v>2.5224</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5142</v>
+        <v>0.0578</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7257</v>
+        <v>-0.0954</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2398</v>
+        <v>0.1531</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8358</v>
+        <v>0.2821</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4477</v>
+        <v>2.7298</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6119</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. TCHIRAKADZE</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1849</v>
+        <v>2.1468</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8664</v>
+        <v>-0.4438</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3186</v>
+        <v>2.5906</v>
       </c>
       <c r="G5" t="n">
-        <v>2.871</v>
+        <v>0.7055</v>
       </c>
       <c r="H5" t="n">
-        <v>2.2393</v>
+        <v>2.376</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6318</v>
+        <v>-1.6706</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8187</v>
+        <v>1.4145</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6364</v>
+        <v>2.1174</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1823</v>
+        <v>-0.7029</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9477</v>
+        <v>-0.709</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3971</v>
+        <v>0.2587</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5506</v>
+        <v>-0.9677</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7761</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7463</v>
+        <v>3.2985</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5204</v>
+        <v>0.1876</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6046</v>
+        <v>-0.4254</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.613</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9418</v>
+        <v>1.8358</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3776</v>
+        <v>2.4477</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5642</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8848</v>
+        <v>1.3397</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3674</v>
+        <v>0.7678</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5174</v>
+        <v>0.5719</v>
       </c>
       <c r="G6" t="n">
         <v>0.1934</v>
@@ -922,13 +922,13 @@
         <v>1.1642</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4729</v>
+        <v>-0.0179</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5451</v>
+        <v>-0.1447</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0722</v>
+        <v>0.1267</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. PUNZANO VIEDMA</t>
+          <t>F. MORENO GUTIERREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.468</v>
+        <v>-0.4438</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8078</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3398</v>
+        <v>0.2915</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7217</v>
+        <v>-1.6086</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3213</v>
+        <v>-0.7333</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4004</v>
+        <v>-0.8753</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6261</v>
+        <v>-0.1824</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0412</v>
+        <v>-0.2636</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6673</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0956</v>
+        <v>-1.4262</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3625</v>
+        <v>-0.4696</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2669</v>
+        <v>-0.9565</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3881</v>
+        <v>0.9702</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3881</v>
+        <v>1.9403</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1821</v>
+        <v>-0.3696</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1817</v>
+        <v>-0.429</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0004</v>
+        <v>0.0595</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0478</v>
+        <v>0.5642</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.8462</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0478</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SHIELDS</t>
+          <t>T. PUNZANO VIEDMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6296</v>
+        <v>-0.5225</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2004</v>
+        <v>-0.8078</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4292</v>
+        <v>0.2853</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1334</v>
+        <v>-0.7217</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3075</v>
+        <v>-0.3213</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1741</v>
+        <v>-0.4004</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5649</v>
+        <v>-0.6261</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6055</v>
+        <v>0.0412</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0406</v>
+        <v>-0.6673</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5685</v>
+        <v>-0.0956</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7019</v>
+        <v>-0.3625</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1335</v>
+        <v>0.2669</v>
       </c>
       <c r="P8" t="n">
         <v>0.3881</v>
@@ -1078,28 +1078,28 @@
         <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7277</v>
+        <v>-0.2366</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3645</v>
+        <v>-0.1817</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3632</v>
+        <v>-0.055</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6119</v>
+        <v>0.0478</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6119</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. MORENO GUTIERREZ</t>
+          <t>D. SHIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9354</v>
+        <v>-1.0934</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.336</v>
+        <v>-0.5007</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4006</v>
+        <v>-0.5927</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6086</v>
+        <v>-1.1334</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7333</v>
+        <v>-1.3075</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8753</v>
+        <v>0.1741</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1824</v>
+        <v>-0.5649</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2636</v>
+        <v>-0.6055</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0406</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4262</v>
+        <v>-0.5685</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4696</v>
+        <v>-0.7019</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9565</v>
+        <v>0.1335</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9702</v>
+        <v>0.3881</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9403</v>
+        <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8611</v>
+        <v>0.2638</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0296</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1685</v>
+        <v>0.1996</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5642</v>
+        <v>-0.6119</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8462</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2821</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7453</v>
+        <v>-2.8459</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6245</v>
+        <v>-2.0249</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1208</v>
+        <v>-0.821</v>
       </c>
       <c r="G10" t="n">
         <v>-4.8593</v>
@@ -1234,13 +1234,13 @@
         <v>3.8806</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0439</v>
+        <v>-0.0567</v>
       </c>
       <c r="T10" t="n">
-        <v>0.609</v>
+        <v>0.2086</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.2652</v>
       </c>
       <c r="V10" t="n">
         <v>2.0701</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7702</v>
+        <v>-3.5695</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.0451</v>
+        <v>-5.5446</v>
       </c>
       <c r="F11" t="n">
-        <v>2.275</v>
+        <v>1.9752</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5602</v>
@@ -1312,13 +1312,13 @@
         <v>1.7463</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.395</v>
+        <v>-0.1943</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9085</v>
+        <v>-0.408</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5135</v>
+        <v>0.2137</v>
       </c>
       <c r="V11" t="n">
         <v>1.3194</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0713</v>
+        <v>-5.5079</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.4893</v>
+        <v>-5.3892</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.582</v>
+        <v>-0.1187</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2753</v>
@@ -1390,13 +1390,13 @@
         <v>3.1045</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4661</v>
+        <v>0.0973</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2412</v>
+        <v>-0.1411</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.225</v>
+        <v>0.2384</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5537</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8442000000000007</v>
+        <v>-0.8440000000000021</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.303999999999998</v>
+        <v>-6.304</v>
       </c>
       <c r="F13" t="n">
-        <v>5.46</v>
+        <v>5.460000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-8.424099999999999</v>
@@ -1450,7 +1450,7 @@
         <v>-6.5898</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.475000000000001</v>
+        <v>-8.475</v>
       </c>
       <c r="N13" t="n">
         <v>-2.2741</v>
@@ -1468,13 +1468,13 @@
         <v>22.3137</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1235000000000001</v>
+        <v>0.1234</v>
       </c>
       <c r="T13" t="n">
         <v>-1.3799</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5032</v>
+        <v>1.5031</v>
       </c>
       <c r="V13" t="n">
         <v>3.5762</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.1373</v>
+        <v>9.3652</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1915</v>
+        <v>5.0924</v>
       </c>
       <c r="F14" t="n">
-        <v>3.9457</v>
+        <v>4.2728</v>
       </c>
       <c r="G14" t="n">
         <v>5.9673</v>
@@ -1546,13 +1546,13 @@
         <v>3.6866</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5888</v>
+        <v>-0.3609</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.5142</v>
+        <v>-0.6133</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0747</v>
+        <v>0.2524</v>
       </c>
       <c r="V14" t="n">
         <v>1.4304</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8031</v>
+        <v>2.5761</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.91</v>
+        <v>-0.8099</v>
       </c>
       <c r="F15" t="n">
-        <v>3.7131</v>
+        <v>3.386</v>
       </c>
       <c r="G15" t="n">
         <v>3.7429</v>
@@ -1624,13 +1624,13 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9327</v>
+        <v>0.7058</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0011</v>
+        <v>0.1012</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9316</v>
+        <v>0.6046</v>
       </c>
       <c r="V15" t="n">
         <v>0.0678</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. GACIC</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.259</v>
+        <v>1.0695</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2262</v>
+        <v>-0.795</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0328</v>
+        <v>1.8645</v>
       </c>
       <c r="G16" t="n">
-        <v>0.851</v>
+        <v>2.2729</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0766</v>
+        <v>-0.0305</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9276</v>
+        <v>2.3034</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2995</v>
+        <v>1.541</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6221</v>
+        <v>0.1607</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6774</v>
+        <v>1.3803</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4485</v>
+        <v>0.732</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6987</v>
+        <v>-0.1912</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2502</v>
+        <v>0.9231</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3881</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.2985</v>
+        <v>-2.1344</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9105</v>
+        <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9289</v>
+        <v>0.3026</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1552</v>
+        <v>-0.2016</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7737000000000001</v>
+        <v>0.5042</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1329</v>
+        <v>-1.506</v>
       </c>
       <c r="W16" t="n">
-        <v>2.0701</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.203</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>S. GACIC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6707</v>
+        <v>0.9943</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8512</v>
+        <v>0.1251</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5219</v>
+        <v>0.8692</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6723</v>
+        <v>0.851</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0727</v>
+        <v>-0.0766</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4004</v>
+        <v>0.9276</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4546</v>
+        <v>1.2995</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6447</v>
+        <v>0.6221</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1901</v>
+        <v>0.6774</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7823</v>
+        <v>-0.4485</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.572</v>
+        <v>-0.6987</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7897</v>
+        <v>0.2502</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3881</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3284</v>
+        <v>-3.2985</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7164</v>
+        <v>2.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0253</v>
+        <v>0.6642</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7301</v>
+        <v>0.0541</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2952</v>
+        <v>0.6102</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.4149</v>
+        <v>-0.1329</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.7075</v>
+        <v>2.0701</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2925</v>
+        <v>-2.203</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3783</v>
+        <v>0.7971</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8951</v>
+        <v>-1.7521</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2734</v>
+        <v>2.5492</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2729</v>
+        <v>0.6723</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0305</v>
+        <v>1.0727</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3034</v>
+        <v>-0.4004</v>
       </c>
       <c r="J18" t="n">
-        <v>1.541</v>
+        <v>1.4546</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1607</v>
+        <v>2.6447</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3803</v>
+        <v>-1.1901</v>
       </c>
       <c r="M18" t="n">
-        <v>0.732</v>
+        <v>-0.7823</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1912</v>
+        <v>-1.572</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9231</v>
+        <v>0.7897</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.3881</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1344</v>
+        <v>-2.3284</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1344</v>
+        <v>2.7164</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6113</v>
+        <v>0.1517</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3017</v>
+        <v>-0.1708</v>
       </c>
       <c r="U18" t="n">
-        <v>0.913</v>
+        <v>0.3225</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.506</v>
+        <v>-0.4149</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.7075</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.506</v>
+        <v>0.2925</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5021</v>
+        <v>0.4476</v>
       </c>
       <c r="E19" t="n">
         <v>-0.0194</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5215</v>
+        <v>0.467</v>
       </c>
       <c r="G19" t="n">
         <v>0.5026</v>
@@ -1936,13 +1936,13 @@
         <v>0.194</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1945</v>
+        <v>-0.249</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1339</v>
+        <v>-0.1884</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1086</v>
+        <v>-0.499</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0375</v>
+        <v>0.463</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.071</v>
+        <v>-0.962</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4183</v>
@@ -2092,13 +2092,13 @@
         <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2425</v>
+        <v>0.367</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1817</v>
+        <v>0.3188</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0608</v>
+        <v>0.0482</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2239</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7863</v>
+        <v>-1.6227</v>
       </c>
       <c r="E22" t="n">
         <v>-0.6388</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1475</v>
+        <v>-0.984</v>
       </c>
       <c r="G22" t="n">
         <v>1.0418</v>
@@ -2170,13 +2170,13 @@
         <v>0.194</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.546</v>
+        <v>-0.3824</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1211</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4248</v>
+        <v>-0.2613</v>
       </c>
       <c r="V22" t="n">
         <v>-1.506</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2439</v>
+        <v>-1.8802</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8678</v>
+        <v>-0.6676</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3761</v>
+        <v>-1.2126</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9446</v>
@@ -2248,13 +2248,13 @@
         <v>0.7761</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8611</v>
+        <v>-0.4974</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3028</v>
+        <v>-0.1026</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5583</v>
+        <v>-0.3948</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2143</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1013</v>
+        <v>-4.4011</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3431</v>
+        <v>-2.9427</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7582</v>
+        <v>-1.4584</v>
       </c>
       <c r="G24" t="n">
         <v>-3.9664</v>
@@ -2326,13 +2326,13 @@
         <v>2.7164</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2548</v>
+        <v>-0.5546</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0902</v>
+        <v>-0.6898</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1646</v>
+        <v>0.1352</v>
       </c>
       <c r="V24" t="n">
         <v>1.4782</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.1099</v>
+        <v>-6.4464</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.9643</v>
+        <v>-4.1645</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.1455</v>
+        <v>-2.2818</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7408</v>
@@ -2404,13 +2404,13 @@
         <v>0.9702</v>
       </c>
       <c r="S25" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.2703</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1828</v>
+        <v>-0.0174</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1166</v>
+        <v>-0.2529</v>
       </c>
       <c r="V25" t="n">
         <v>-0.5546</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8440999999999992</v>
+        <v>0.8439999999999985</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.460000000000001</v>
+        <v>-5.46</v>
       </c>
       <c r="F26" t="n">
-        <v>6.304099999999998</v>
+        <v>6.303900000000001</v>
       </c>
       <c r="G26" t="n">
         <v>8.424300000000001</v>
@@ -2482,13 +2482,13 @@
         <v>18.4329</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1232999999999996</v>
+        <v>-0.1233</v>
       </c>
       <c r="T26" t="n">
         <v>-1.5031</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3798</v>
+        <v>1.3799</v>
       </c>
       <c r="V26" t="n">
         <v>-3.576199999999999</v>
